--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -314,7 +314,7 @@
         <t>예: act_1234567890</t>
       </text>
     </comment>
-    <comment ref="L4" authorId="0" shapeId="0">
+    <comment ref="M4" authorId="0" shapeId="0">
       <text>
         <t>신규/초기 백필이면 Y, 일반 운영은 N 권장</t>
       </text>
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -625,7 +625,7 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="52" customWidth="1" min="13" max="13"/>
   </cols>
@@ -647,7 +647,7 @@
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>현재 업로드 데이터는 네이버 계정만 반영했습니다. 이름에 " GFA"가 붙은 행은 네이버 GFA 계정입니다.</t>
+          <t>비즈머니는 기본적으로 계정별로 따로 수집합니다. 공유 잔액일 때만 비즈머니 수집방식=shared + 같은 그룹키를 사용하세요.</t>
         </is>
       </c>
     </row>
@@ -704,15 +704,20 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
+          <t>비즈머니 수집방식</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
           <t>수집기본값</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>첫날 구조동기화</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -763,17 +768,22 @@
       </c>
       <c r="K5" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -822,17 +832,22 @@
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L6" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M6" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -881,17 +896,22 @@
       </c>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L7" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -940,17 +960,22 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L8" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N8" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -999,17 +1024,22 @@
       </c>
       <c r="K9" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M9" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1088,22 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N10" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1152,22 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M11" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1216,22 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1235,17 +1280,22 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1344,22 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L14" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1408,22 @@
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1412,17 +1472,22 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L16" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1536,22 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M17" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1530,17 +1600,22 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1589,17 +1664,22 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M19" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1648,17 +1728,22 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L20" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1792,22 @@
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L21" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M21" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1856,22 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L22" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1825,17 +1920,22 @@
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M23" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M23" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1884,17 +1984,22 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L24" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M24" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M24" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -1943,17 +2048,22 @@
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M25" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2002,17 +2112,22 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L26" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2176,22 @@
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M27" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2240,22 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L28" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M28" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2304,22 @@
       </c>
       <c r="K29" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M29" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2238,17 +2368,22 @@
       </c>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L30" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M30" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2297,17 +2432,22 @@
       </c>
       <c r="K31" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M31" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2496,22 @@
       </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L32" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M32" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N32" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2560,22 @@
       </c>
       <c r="K33" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M33" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M33" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2474,17 +2624,22 @@
       </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L34" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M34" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M34" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2688,22 @@
       </c>
       <c r="K35" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L35" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N35" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2752,22 @@
       </c>
       <c r="K36" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L36" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M36" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2651,17 +2816,22 @@
       </c>
       <c r="K37" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L37" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M37" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M37" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2710,17 +2880,22 @@
       </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L38" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M38" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M38" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N38" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2944,22 @@
       </c>
       <c r="K39" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L39" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M39" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M39" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2828,17 +3008,22 @@
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M40" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2887,17 +3072,22 @@
       </c>
       <c r="K41" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M41" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M41" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N41" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -2946,17 +3136,22 @@
       </c>
       <c r="K42" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L42" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N42" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3005,17 +3200,22 @@
       </c>
       <c r="K43" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L43" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M43" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M43" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N43" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3064,17 +3264,22 @@
       </c>
       <c r="K44" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L44" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M44" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N44" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3328,22 @@
       </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L45" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M45" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M45" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3182,17 +3392,22 @@
       </c>
       <c r="K46" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L46" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M46" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M46" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N46" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3456,22 @@
       </c>
       <c r="K47" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L47" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M47" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M47" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N47" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3300,17 +3520,22 @@
       </c>
       <c r="K48" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L48" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M48" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N48" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3359,17 +3584,22 @@
       </c>
       <c r="K49" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L49" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M49" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M49" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N49" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3418,17 +3648,22 @@
       </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L50" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M50" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M50" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N50" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3477,17 +3712,22 @@
       </c>
       <c r="K51" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L51" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M51" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M51" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N51" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3536,17 +3776,22 @@
       </c>
       <c r="K52" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L52" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M52" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N52" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3595,17 +3840,22 @@
       </c>
       <c r="K53" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M53" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M53" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N53" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3654,17 +3904,22 @@
       </c>
       <c r="K54" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L54" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M54" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3968,22 @@
       </c>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L55" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M55" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M55" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N55" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3772,17 +4032,22 @@
       </c>
       <c r="K56" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L56" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M56" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M56" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N56" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3831,17 +4096,22 @@
       </c>
       <c r="K57" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L57" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M57" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M57" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N57" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3890,17 +4160,22 @@
       </c>
       <c r="K58" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L58" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M58" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M58" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N58" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -3949,17 +4224,22 @@
       </c>
       <c r="K59" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L59" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M59" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N59" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4288,22 @@
       </c>
       <c r="K60" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L60" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M60" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M60" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4067,17 +4352,22 @@
       </c>
       <c r="K61" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L61" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M61" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M61" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N61" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4126,17 +4416,22 @@
       </c>
       <c r="K62" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L62" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M62" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M62" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N62" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4185,17 +4480,22 @@
       </c>
       <c r="K63" s="18" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L63" s="18" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M63" s="19" t="inlineStr">
-        <is>
-          <t>네이버 검색광고 계정</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M63" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" s="19" t="inlineStr">
+        <is>
+          <t>네이버 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4239,22 +4539,27 @@
       <c r="I64" s="20" t="inlineStr"/>
       <c r="J64" s="21" t="inlineStr">
         <is>
-          <t>로베라</t>
+          <t>로베라 GFA</t>
         </is>
       </c>
       <c r="K64" s="21" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L64" s="21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M64" s="22" t="inlineStr">
-        <is>
-          <t>네이버 GFA 계정 / 비즈머니는 그룹키 기준으로 검색광고와 함께 관리 / 성과는 별도 수집</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N64" s="22" t="inlineStr">
+        <is>
+          <t>네이버 GFA 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4298,22 +4603,27 @@
       <c r="I65" s="20" t="inlineStr"/>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>한우이츠</t>
+          <t>한우이츠 GFA</t>
         </is>
       </c>
       <c r="K65" s="21" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L65" s="21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M65" s="22" t="inlineStr">
-        <is>
-          <t>네이버 GFA 계정 / 비즈머니는 그룹키 기준으로 검색광고와 함께 관리 / 성과는 별도 수집</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M65" s="21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N65" s="22" t="inlineStr">
+        <is>
+          <t>네이버 GFA 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4357,22 +4667,27 @@
       <c r="I66" s="20" t="inlineStr"/>
       <c r="J66" s="21" t="inlineStr">
         <is>
-          <t>시종도어</t>
+          <t>시종도어 GFA</t>
         </is>
       </c>
       <c r="K66" s="21" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L66" s="21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M66" s="22" t="inlineStr">
-        <is>
-          <t>네이버 GFA 계정 / 비즈머니는 그룹키 기준으로 검색광고와 함께 관리 / 성과는 별도 수집</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M66" s="21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N66" s="22" t="inlineStr">
+        <is>
+          <t>네이버 GFA 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4416,22 +4731,27 @@
       <c r="I67" s="20" t="inlineStr"/>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>더마드라이</t>
+          <t>더마드라이 GFA</t>
         </is>
       </c>
       <c r="K67" s="21" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="L67" s="21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M67" s="22" t="inlineStr">
-        <is>
-          <t>네이버 GFA 계정 / 비즈머니는 그룹키 기준으로 검색광고와 함께 관리 / 성과는 별도 수집</t>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="M67" s="21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N67" s="22" t="inlineStr">
+        <is>
+          <t>네이버 GFA 계정 / 비즈머니는 기본적으로 계정별 별도 수집 / 공유 잔액이면 shared로 직접 변경</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4762,7 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="12">
     <dataValidation sqref="C5:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=코드값!$A$2:$A$3</formula1>
     </dataValidation>
@@ -4470,6 +4790,15 @@
     <dataValidation sqref="D5:D1000 L5:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation sqref="K5:K67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=코드값!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="L5:L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=코드값!$D$2:$D$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5:M67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=코드값!$E$2:$E$3</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4499,7 +4828,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>1) 한 업체에 검색광고(SA)와 GFA가 모두 있으면 행을 2개로 만듭니다.</t>
+          <t>1) 한 업체에 검색광고(SA)와 GFA가 모두 있어도 비즈머니는 기본적으로 각각 따로 봅니다.</t>
         </is>
       </c>
     </row>
@@ -4513,33 +4842,37 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>3) 업체그룹명과 비즈머니 그룹키는 같은 업체의 SA/GFA에 동일하게 적습니다.</t>
+          <t>3) 비즈머니 수집방식은 기본값이 separate(계정별 개별 수집)입니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>4) 비즈머니는 그룹키 기준으로 함께 관리하고, 성과 데이터는 계정표시명(행) 기준으로 따로 수집합니다.</t>
+          <t>4) 실제로 같은 비즈머니를 쓰는 계정만 shared로 바꾸고 같은 비즈머니 그룹키를 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>5) 메타를 붙일 때는 새 행을 추가하고 플랫폼=meta, 네이버 매체유형=meta 로 입력합니다.</t>
+          <t>5) separate일 때는 비즈머니 그룹키가 같아도 묶지 않습니다. 그룹키는 참고용이거나 계정명 그대로 두면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>6) 토큰은 이 파일에 적지 말고 .env 또는 GitHub Secrets에 넣습니다.</t>
+          <t>6) 성과 데이터는 항상 계정표시명(행) 기준으로 따로 수집합니다.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24" t="n"/>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>7) 토큰/시크릿은 이 파일에 적지 말고 .env 또는 GitHub Secrets에 저장합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
@@ -4638,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4660,10 +4993,15 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
+          <t>bizmoney_mode</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
           <t>collect_mode</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>sync_dim_first_day</t>
         </is>
@@ -4682,10 +5020,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>naver_only</t>
+          <t>separate</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>naver_only</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4704,10 +5047,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>meta_only</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4719,7 +5067,7 @@
           <t>naver,meta</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>both</t>
         </is>

--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D857C32-77B9-4752-B7A0-9EC3DA25866C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A32B75F9-D332-4E64-ABCE-BC4B521D5875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="3465" windowWidth="33330" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="계정마스터" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">계정마스터!$A$4:$M$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">원본데이터!$A$1:$C$64</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -135,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="185">
   <si>
     <t>광고 계정 마스터 (네이버/메타 공용)</t>
   </si>
@@ -689,6 +702,10 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>금호주택</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1168,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3837,6 +3854,42 @@
       </c>
       <c r="N68" s="6"/>
     </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="6">
+        <v>4335571</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:M67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
@@ -3846,7 +3899,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="L5:L1000 D5:D1000" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D1000 L5:L1000" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E5:E1000" xr:uid="{00000000-0002-0000-0000-000005000000}">
@@ -3868,7 +3921,7 @@
           <x14:formula1>
             <xm:f>코드값!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C5:C67 C69:C200</xm:sqref>
+          <xm:sqref>C5:C67 C70:C200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>

--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3002CCC9-D380-420D-9CB2-A7D4A25B9B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCAF047-0AEF-454C-93BE-8332C960ECF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="계정마스터" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <sheet name="원본데이터" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -35,6 +40,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>Y면 사용, N이면 수집 제외</t>
         </r>
@@ -47,6 +54,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>naver / meta / naver,meta 중 선택</t>
         </r>
@@ -59,6 +68,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>기본 수집 실행값. 필요 시 workflow에서 덮어쓸 수 있음</t>
         </r>
@@ -71,6 +82,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>예: 1234567</t>
         </r>
@@ -83,6 +96,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>내부 운영용 식별자. 없으면 비워도 됨</t>
         </r>
@@ -95,6 +110,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>예: act_1234567890</t>
         </r>
@@ -107,6 +124,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
           </rPr>
           <t>신규/초기 백필이면 Y, 일반 운영은 N 권장</t>
         </r>
@@ -117,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="184">
   <si>
     <t>광고 계정 마스터 (네이버/메타 공용)</t>
   </si>
@@ -667,13 +686,17 @@
   <si>
     <t>집콕</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵이득마켓</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,6 +759,13 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -837,6 +867,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -846,12 +882,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,6 +944,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE041205-6F16-360D-A6F7-4FCA48271A90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -1104,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1122,55 +1206,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3813,10 +3897,10 @@
       <c r="A70" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="16" t="s">
         <v>182</v>
       </c>
       <c r="D70" s="6" t="s">
@@ -3831,7 +3915,7 @@
       <c r="G70">
         <v>3492778</v>
       </c>
-      <c r="J70" s="21" t="s">
+      <c r="J70" s="17" t="s">
         <v>182</v>
       </c>
       <c r="K70" s="6" t="s">
@@ -3841,6 +3925,41 @@
         <v>23</v>
       </c>
       <c r="M70" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="5">
+        <v>2535578</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3852,7 +3971,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="D5:D1000 L5:L1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D1000 G71 L5:L1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E5:E1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
